--- a/doc/_static/example-files/PMHC-4-1-intake.xlsx
+++ b/doc/_static/example-files/PMHC-4-1-intake.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennib/Work/git/PMHC/spec/doc/_static/example-files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E20A3FD-700B-4941-858A-D7152CEB5FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,7 @@
     <sheet name="Intakes" sheetId="4" r:id="rId4"/>
     <sheet name="IAR-DST" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -335,8 +341,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,13 +379,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -417,7 +431,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -451,6 +465,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -485,9 +500,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -660,11 +676,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -680,12 +696,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -694,11 +710,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -733,7 +749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -759,7 +775,7 @@
         <v>9099999</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -791,11 +807,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -830,7 +846,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -862,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -894,7 +910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -926,7 +942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -958,7 +974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -990,7 +1006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1028,11 +1044,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1076,7 +1092,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1117,7 +1133,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1158,7 +1174,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1199,7 +1215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1240,7 +1256,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1281,7 +1297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1322,7 +1338,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1363,7 +1379,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1404,7 +1420,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1445,7 +1461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1486,7 +1502,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1524,11 +1540,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1575,7 +1591,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1619,7 +1635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1663,7 +1679,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1707,7 +1723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1751,7 +1767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1795,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1839,7 +1855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1883,7 +1899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1927,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1971,7 +1987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2015,7 +2031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
